--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Tableau</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Data Lake, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,164 +496,164 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c10613312eae7d7</t>
+          <t>https://www.indeed.com/viewjob?jk=99977a748ac9e602</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Application Developer</t>
+          <t>Software Engineer III - Admin Center</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, BigQuery, Synapse, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81dac51ac780b98f</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f33f4a77a6827e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Premier Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, AWS SageMaker, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce7de4b4a1ae62af</t>
+          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Applied AI Strategist &amp; Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PAR Technology</t>
+          <t>West Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Glue, MLflow, CI/CD, Git, Databricks</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB, Prompt Engineering</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de950818ae0f1c11</t>
+          <t>https://www.indeed.com/viewjob?jk=18f600dcfbb427d9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Agent Developer</t>
+          <t>Senior AI/ML Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4da0d5c78cb9198e</t>
+          <t>https://www.indeed.com/viewjob?jk=1cbad5d820211d0e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI/ML Engineer - Software Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Terraform, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3267f4ddbfd71ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d062f6a5ff69670e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SENIOR RESEARCH SCIENTIST - NETWORK SYSTEMS</t>
+          <t>Machine Learning Ops Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Sheetz</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Red Bank, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,217 +706,147 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dcde764a9784fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e15bc0bb0d3d46</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Content Partner Engineer, Youtube</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Studio McGee</t>
+          <t>Youtube</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fce98418ec68193</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3ee08ae5c940ef</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Content Partner Engineer, Youtube</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RingCentral</t>
+          <t>Youtube</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Bruno, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Gemini, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec82a6f78cba7d8</t>
+          <t>https://www.indeed.com/viewjob?jk=67f85d2dbf7a13c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Summer Intern - Global DevOps</t>
+          <t>Content Partner Engineer, Youtube</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Youtube</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Gemini, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59ea855276042fd</t>
+          <t>https://www.indeed.com/viewjob?jk=9255c790c56d213e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics team</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Hugging Face, Synapse, Docker, Kubernetes, AKS, Terraform, Databricks, Power BI, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a1f0248c4ddbf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Machine Learning Developer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Cortex, MLflow, Snowflake, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1464c0384a332a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Full-Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Mosaic Company</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Renton, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56e05cf3f964678c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3a46ad0f0c637af</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java Development Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Data Lake, Kubernetes</t>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Git, BigQuery, Kafka, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99977a748ac9e602</t>
+          <t>https://www.indeed.com/viewjob?jk=044788dae086d6fb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Admin Center</t>
+          <t>Senior Data Scientist- Fractional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>HiddenLevers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, EC2, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Snowflake, Databricks, Hadoop, Tableau, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f33f4a77a6827e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17bc1c30c5ee7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sr Software Engineer - Live and Linear Tooling</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Premier Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL</t>
+          <t>Data Scientist, S3, EC2, Kinesis, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2728e69028426d36</t>
+          <t>https://www.indeed.com/viewjob?jk=3813402781f4a5a6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Applied AI Strategist &amp; Developer</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>West Health</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB, Prompt Engineering</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f600dcfbb427d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6c380f03b9eebc0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer / Data Scientist</t>
+          <t>Snowflake Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, PySpark</t>
+          <t>RAG, Apache Airflow, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cbad5d820211d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Software Engineer III</t>
+          <t>Sr. SAS Modeler and Programmer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Key Marketing Advantage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newtown, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
+          <t>RAG, Redshift, Docker, Git, Redshift, Hadoop, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,182 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d062f6a5ff69670e</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Machine Learning Ops Engineer II</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sheetz</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e15bc0bb0d3d46</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Content Partner Engineer, Youtube</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Youtube</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3ee08ae5c940ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Content Partner Engineer, Youtube</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Youtube</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Bruno, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67f85d2dbf7a13c6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Content Partner Engineer, Youtube</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Youtube</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9255c790c56d213e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Science Senior Associate - Card Data &amp; Analytics team</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3a46ad0f0c637af</t>
+          <t>https://www.indeed.com/viewjob?jk=118073b5d965fe4a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Development Engineer</t>
+          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Jackson National Life Insurance Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Git, BigQuery, Kafka, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=044788dae086d6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist- Fractional</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HiddenLevers</t>
+          <t>Stefanini North America and APAC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Snowflake, Databricks, Hadoop, Tableau, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17bc1c30c5ee7</t>
+          <t>https://www.indeed.com/viewjob?jk=47240e8a58c54b42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Live and Linear Tooling</t>
+          <t>Python Backend Platform Engineer (AI Software)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>QuadCode</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Kinesis, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3813402781f4a5a6</t>
+          <t>https://www.indeed.com/viewjob?jk=62a1668fabf84cd4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>ML / AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Gradient</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Renton, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Git, Python, R, Java</t>
+          <t>AI Engineer, FAISS, Pinecone, TensorFlow, PyTorch, OpenCV, Docker, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c380f03b9eebc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ffd643a1e4a05c67</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect (Remote)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsford, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Apache Airflow, CI/CD, Jenkins, Git, Snowflake, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50af2306075e0747</t>
+          <t>https://www.indeed.com/viewjob?jk=269aac998435f13b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. SAS Modeler and Programmer</t>
+          <t>Senior Decision Scientist – Fulfillment Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Key Marketing Advantage</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newtown, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Git, Redshift, Hadoop, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, Data Lake, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,42 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118073b5d965fe4a</t>
+          <t>https://www.indeed.com/viewjob?jk=abb975b89646ed50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Slip Robotics</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Snowflake, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PART-TIME Strategic Support Associate, Data and Artificial Intelligence</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jackson National Life Insurance Company</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=479fc3779fa1d9b4</t>
+          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer (Clickhouse)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stefanini North America and APAC</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Databricks, PySpark, Python</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47240e8a58c54b42</t>
+          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python Backend Platform Engineer (AI Software)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>QuadCode</t>
+          <t>HirexHire</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62a1668fabf84cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=4193cafebe6ed1d7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ML / AI Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gradient</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, FAISS, Pinecone, TensorFlow, PyTorch, OpenCV, Docker, Python, R, Scala</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd643a1e4a05c67</t>
+          <t>https://www.indeed.com/viewjob?jk=9f65e3ddb926a918</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsford, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Java</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269aac998435f13b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a72e4b721107091</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Decision Scientist – Fulfillment Analytics</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,637 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb975b89646ed50</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d935bd584fe6c7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>Databricks / PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Slip Robotics</t>
+          <t>Doran Jones</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, CI/CD, Git, Databricks, PySpark, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer – SaaS Platform</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Principle Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FORTNA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c58be6757539c055</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Komatsu</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37db36c692caed69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Agentic AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=339514ab21c28c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Agentic AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5c9767a1b8c5fb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Agentic AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bff92c1bd79d39a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Agentic AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9415c7efa886573b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Princ Engr-Software Devt</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=675cc9b1aaf0ab1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Solutions Engineer, Global</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9be3a3cc76a44585</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Site Reliability</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Upstart</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CI/CD, Git, Snowflake, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=235773020d8ae10f</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25e1d73a8e28efa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Helixtachinc</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Stockton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6886d6f207c8d5e7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, RAG, Redshift, Docker, Kubernetes, Snowflake, Databricks, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088655e3e3b8844d</t>
+          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Clickhouse)</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Basis Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, PostgreSQL, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d35f74fc9491129</t>
+          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior, Software Engineer - Fullstack</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HirexHire</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, PostgreSQL</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4193cafebe6ed1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f65e3ddb926a918</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a72e4b721107091</t>
+          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Consortium Cloud Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Doheny Eye Institute</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, EC2, MLflow, Docker, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d935bd584fe6c7</t>
+          <t>https://www.indeed.com/viewjob?jk=42c26757ecbe72b3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks / PySpark Data Engineer</t>
+          <t>Data Engineer III - Data &amp; AI Enablement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Doran Jones</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, CI/CD, Git, Databricks, PySpark, Tableau, Python, SQL</t>
+          <t>Generative AI, RAG, Synapse, MLflow, Git, Databricks, PySpark, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9ee957e5ec3e951</t>
+          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – SaaS Platform</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2bee0c494f3ad24</t>
+          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Scala Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Railroad19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7608ed5bf8f408b</t>
+          <t>https://www.indeed.com/viewjob?jk=711634f6b2e296f9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>Generative AI, RAG, Jenkins, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=048f60b12aa9a7c6</t>
+          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Clinical Trial Data</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, AWS SageMaker, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc4b686f19aac3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d60bfca02adda5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8021ad4fe6bcc63</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba47d9528dfd9c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Hadoop, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2111c5e7eab910a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0940a2205966afdb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer (AI/ML) Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec83795e8e9d3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc93f8f9f50b87d0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Principle Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FORTNA</t>
+          <t>Global Technology Solutions Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Gemini, BigQuery, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,322 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c58be6757539c055</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Komatsu</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37db36c692caed69</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Agentic AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=339514ab21c28c3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Agentic AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5c9767a1b8c5fb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Agentic AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bff92c1bd79d39a</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Agentic AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9415c7efa886573b</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Princ Engr-Software Devt</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Verizon</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=675cc9b1aaf0ab1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Solutions Engineer, Global</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Vantage Data Centers</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9be3a3cc76a44585</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Site Reliability</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Upstart</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=25e1d73a8e28efa2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Helixtachinc</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Stockton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6886d6f207c8d5e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b64a14a30cbcea36</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IS Data Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CareOregon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Westlake Village, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Docker, Kubernetes, Snowflake, Databricks, Redshift, Tableau, Power BI</t>
+          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125db3e6bdb4e943</t>
+          <t>https://www.indeed.com/viewjob?jk=5af157c666d12c35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Basis Technologies</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Snowflake, Kafka, PostgreSQL, MySQL, MongoDB, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d626797e376230a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior, Software Engineer - Fullstack</t>
+          <t>Sr. Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Jenkins, Git, Kafka, MySQL, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb36340453827bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=91c0d2b3557f0bb9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Artificial Intelligence Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bfb8b0bbcb095a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad107287a5b5ffd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Integration Engineer (Entry Level)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e30a8b267fbd675e</t>
+          <t>https://www.indeed.com/viewjob?jk=71e704763365b976</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Consortium Cloud Engineer</t>
+          <t>Integration Engineer (Entry Level)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Doheny Eye Institute</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, EC2, MLflow, Docker, Python, R</t>
+          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42c26757ecbe72b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8528917b56cf4496</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer III - Data &amp; AI Enablement</t>
+          <t>Senior Software Engineer, Backend Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Jacobian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Synapse, MLflow, Git, Databricks, PySpark, Kafka, SQL, R</t>
+          <t>RAG, S3, Kubernetes, CI/CD, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d761d2ecf33cf983</t>
+          <t>https://www.indeed.com/viewjob?jk=d352fcdf6b72a0c4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Python Software Engineer - Schaumburg, IL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, NoSQL, SQL, R, Java</t>
+          <t>EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a556c0c0b65e6c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Scala Software Engineer</t>
+          <t>Software &amp; Data Engineer – Financial Technology - Launch Program</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Railroad19</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Union, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL, R, Scala</t>
+          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711634f6b2e296f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c4b99ef1a554f97</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Covered Insurance Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Jenkins, Terraform, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663cf689cd0cf520</t>
+          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Clinical Trial Data</t>
+          <t>Applied AI Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Kenai Defense</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Somerset, KY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, Docker, Kubernetes, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Hugging Face, Sentence Transformers, PyTorch, Docker, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d60bfca02adda5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e9db47222995b90</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
+          <t>RAG, TensorFlow, PyTorch, S3, Docker, CI/CD, Terraform, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba47d9528dfd9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b80993c7486f0a43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>TELI.AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Hadoop, Python, R, Scala</t>
+          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0940a2205966afdb</t>
+          <t>https://www.indeed.com/viewjob?jk=5755769f75e71f85</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI/ML) Intern</t>
+          <t>Applied AI Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Kenai Defense</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Hugging Face, Sentence Transformers, PyTorch, Docker, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc93f8f9f50b87d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ffdc015414ef17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Architect / Developer SME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Global Technology Solutions Inc</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, Terraform, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64a14a30cbcea36</t>
+          <t>https://www.indeed.com/viewjob?jk=e592f72a7466ebca</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-19.xlsx
+++ b/daily_matches/job_matches_2026-03-19.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Westlake Village, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, S3, Glue, Athena, Redshift, BigQuery, Synapse, Data Lake, Kinesis</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af157c666d12c35</t>
+          <t>https://www.indeed.com/viewjob?jk=1a207649ab0be82e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, CI/CD, Git, Snowflake, Databricks</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0289d31e08c4fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba6b6774e660f43</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Artificial Intelligence Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91c0d2b3557f0bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2499db08cd7189</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Sr Applied AI Machine Learning Engineer - Claims Data Science</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>24.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, EC2, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad107287a5b5ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe6442929dd09f9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Integration Engineer (Entry Level)</t>
+          <t>Associate Data Engineer- Hyperscale- Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e704763365b976</t>
+          <t>https://www.indeed.com/viewjob?jk=eee1c6c65c9ef5f7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Integration Engineer (Entry Level)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, TensorFlow, Docker, Kubernetes, CI/CD, Git, NoSQL, Python</t>
+          <t>RAG, Dataflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8528917b56cf4496</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d4408cceed11d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Platform</t>
+          <t>Junior AI Applications Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jacobian</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, PostgreSQL, MongoDB, Cassandra, NoSQL, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Mistral, FAISS, Pinecone, Prompt Engineering, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d352fcdf6b72a0c4</t>
+          <t>https://www.indeed.com/viewjob?jk=af0e688d944d5290</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Software Engineer - Schaumburg, IL</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EC2, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, GCP Vertex AI, FastAPI, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e48f7514f4285fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3edac4d73cf2e6d2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software &amp; Data Engineer – Financial Technology - Launch Program</t>
+          <t>DevOps Engineer (Technology Specialist I) - Digital and Technology Partners - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Union, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FastAPI, Docker, Kubernetes, CI/CD, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c4b99ef1a554f97</t>
+          <t>https://www.indeed.com/viewjob?jk=67bd18e00ac68d8b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Covered Insurance Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, CI/CD, Git, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439864a586cda933</t>
+          <t>https://www.indeed.com/viewjob?jk=064b819a652772f2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied AI Data Engineer</t>
+          <t>Sr. Cloud/Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kenai Defense</t>
+          <t>Conagra Brands</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Somerset, KY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Sentence Transformers, PyTorch, Docker, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9db47222995b90</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8cdbdda0b386a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vdrive IT Solutions, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, Docker, CI/CD, Terraform, Python, SQL, R</t>
+          <t>Generative AI, Prompt Engineering, FastAPI, CI/CD, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80993c7486f0a43</t>
+          <t>https://www.indeed.com/viewjob?jk=67166ac5408baa11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Legal &amp; Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TELI.AI</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, S3, R, Scala, A/B Testing</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,77 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5755769f75e71f85</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Applied AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kenai Defense</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Woods Cross, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Hugging Face, Sentence Transformers, PyTorch, Docker, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ffdc015414ef17</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cloud Architect / Developer SME</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e592f72a7466ebca</t>
+          <t>https://www.indeed.com/viewjob?jk=2dbcb3846bcc154e</t>
         </is>
       </c>
     </row>
